--- a/data/lossofsale_sg_manjeri.xlsx
+++ b/data/lossofsale_sg_manjeri.xlsx
@@ -1492,6 +1492,377 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>24</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Rasiya</t>
+        </is>
+      </c>
+      <c r="D26" s="65">
+        <v>9048447818</v>
+      </c>
+      <c t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F26">
+        <is>
+          <t xml:space="preserve">Abdul Hadi Rafeeque</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G26">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H26">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J26">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K26">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>25</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">munsif</t>
+        </is>
+      </c>
+      <c r="D27" s="65">
+        <v>7034655072</v>
+      </c>
+      <c t="inlineStr" r="E27">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F27">
+        <is>
+          <t xml:space="preserve">AKASH VK</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G27">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H27">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I27">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J27">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K27">
+        <is>
+          <t xml:space="preserve">30,32 SUIT PISTA COLOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>26</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">fayis</t>
+        </is>
+      </c>
+      <c r="D28" s="65">
+        <v>9745757744</v>
+      </c>
+      <c t="inlineStr" r="E28">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F28">
+        <is>
+          <t xml:space="preserve">SAJITH K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G28">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H28">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I28">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J28">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K28">
+        <is>
+          <t xml:space="preserve">Required model not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>27</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">AIBEL</t>
+        </is>
+      </c>
+      <c r="D29" s="65">
+        <v>9048093601</v>
+      </c>
+      <c t="inlineStr" r="E29">
+        <is>
+          <t xml:space="preserve">26-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F29">
+        <is>
+          <t xml:space="preserve">SHIBIN RAJ KK</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G29">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H29">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I29">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J29">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K29">
+        <is>
+          <t xml:space="preserve">32 SIZE NEEDED BLACK GOLD WORK SUIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>28</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">UNYOONES</t>
+        </is>
+      </c>
+      <c r="D30" s="65">
+        <v>8156917793</v>
+      </c>
+      <c t="inlineStr" r="E30">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F30">
+        <is>
+          <t xml:space="preserve">AKASH VK</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G30">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H30">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I30">
+        <is>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J30">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K30">
+        <is>
+          <t xml:space="preserve">30 SIZE SKY BLUE SUIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>29</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">JINU ANTO</t>
+        </is>
+      </c>
+      <c r="D31" s="65">
+        <v>8129412435</v>
+      </c>
+      <c t="inlineStr" r="E31">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F31">
+        <is>
+          <t xml:space="preserve">SAJITH K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G31">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H31">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I31">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J31">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K31">
+        <is>
+          <t xml:space="preserve">NAVEY BLUE PLAIN TUXTRUE SUIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>30</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">ILAN</t>
+        </is>
+      </c>
+      <c r="D32" s="65">
+        <v>9495582065</v>
+      </c>
+      <c t="inlineStr" r="E32">
+        <is>
+          <t xml:space="preserve">09-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F32">
+        <is>
+          <t xml:space="preserve">Abdul Hadi Rafeeque</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G32">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H32">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I32">
+        <is>
+          <t xml:space="preserve">RENT TO HIGH</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J32">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K32">
+        <is>
+          <t xml:space="preserve">rent too high</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
